--- a/human_resources_forms/020_portfolio_manager_interview_form--human_resources_forms.xlsx
+++ b/human_resources_forms/020_portfolio_manager_interview_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>aa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>AA</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>aa</t>
+          <t>um</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>UM</t>
         </is>
       </c>
     </row>
@@ -2105,29 +2105,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>pw</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UM</t>
+          <t>PW</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pw</t>
+          <t>microsoft_office</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PW</t>
+          <t>Microsoft Office</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>microsoft_office</t>
+          <t>microsoft_office_suite</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Microsoft Office</t>
+          <t>Microsoft Office Suite</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>microsoft_office_suite</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Microsoft Office Suite</t>
+          <t>Excel</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>word</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Word</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>word</t>
+          <t>powerpoint</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>PowerPoint</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>powerpoint</t>
+          <t>google_docs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PowerPoint</t>
+          <t>Google Docs</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>google_docs</t>
+          <t>google_sheets</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Google Docs</t>
+          <t>Google Sheets</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>google_sheets</t>
+          <t>google_slides</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Google Slides</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>google_slides</t>
+          <t>visio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Google Slides</t>
+          <t>Visio</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>visio</t>
+          <t>adobe_creative_suite</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Visio</t>
+          <t>Adobe Creative Suite</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>adobe_creative_suite</t>
+          <t>adobe_acrobat</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Adobe Creative Suite</t>
+          <t>Adobe Acrobat</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>adobe_acrobat</t>
+          <t>adobe_photoshop</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Adobe Acrobat</t>
+          <t>Adobe Photoshop</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>adobe_photoshop</t>
+          <t>adobe_illustrator</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Adobe Photoshop</t>
+          <t>Adobe Illustrator</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>adobe_illustrator</t>
+          <t>adobe_indesign</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Adobe Illustrator</t>
+          <t>Adobe InDesign</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>adobe_indesign</t>
+          <t>adobe_lightroom</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Adobe InDesign</t>
+          <t>Adobe Lightroom</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>adobe_lightroom</t>
+          <t>adobe_dreamweaver</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Adobe Lightroom</t>
+          <t>Adobe Dreamweaver</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>adobe_dreamweaver</t>
+          <t>adobe_after_effects</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Adobe Dreamweaver</t>
+          <t>Adobe After Effects</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>adobe_after_effects</t>
+          <t>sketchup</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Adobe After Effects</t>
+          <t>Sketchup</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>adobe_illustrator</t>
+          <t>revit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Adobe Illustrator</t>
+          <t>Revit</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sketchup</t>
+          <t>3d_max</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sketchup</t>
+          <t>3D Max</t>
         </is>
       </c>
     </row>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>revit</t>
+          <t>maya</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Revit</t>
+          <t>Maya</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3d_max</t>
+          <t>blender</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3D Max</t>
+          <t>Blender</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>maya</t>
+          <t>autocad</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>AutoCAD</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>blender</t>
+          <t>coreldraw</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Blender</t>
+          <t>CorelDRAW</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>autocad</t>
+          <t>autocad_lt</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AutoCAD</t>
+          <t>AutoCAD LT</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>coreldraw</t>
+          <t>autocad_mep</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CorelDRAW</t>
+          <t>AutoCAD MEP</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>autocad_lt</t>
+          <t>autocad_architecture</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AutoCAD LT</t>
+          <t>AutoCAD Architecture</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>autocad_mep</t>
+          <t>sketchup_pro</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AutoCAD MEP</t>
+          <t>Sketchup Pro</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>autocad_architecture</t>
+          <t>autodesk_inventor</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AutoCAD Architecture</t>
+          <t>Autodesk Inventor</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>autocad_mep</t>
+          <t>revit_mep</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AutoCAD MEP</t>
+          <t>Revit MEP</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sketchup_pro</t>
+          <t>autodesk_revit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sketchup Pro</t>
+          <t>Autodesk Revit</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>autodesk_inventor</t>
+          <t>autocad_electrical</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Autodesk Inventor</t>
+          <t>AutoCAD Electrical</t>
         </is>
       </c>
     </row>
@@ -2666,469 +2666,282 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>revit_mep</t>
+          <t>autocad_civil_3d</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Revit MEP</t>
+          <t>AutoCAD Civil 3D</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>autodesk_revit</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Autodesk Revit</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>autocad_electrical</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AutoCAD Electrical</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>autocad_civil_3d</t>
+          <t>associate's</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AutoCAD Civil 3D</t>
+          <t>Associate's</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>autocad_architecture</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AutoCAD Architecture</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>autocad_civil_3d</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AutoCAD Civil 3D</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>autocad_mep</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AutoCAD MEP</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>coreldraw</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CorelDRAW</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>adobe_photoshop</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Adobe Photoshop</t>
+          <t>Software Development</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>adobe_illustrator</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Adobe Illustrator</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>sketchup</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sketchup</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>revit</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Revit</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>some_college</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Some College</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>associate's</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Associate's</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>bachelor's</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bachelor's</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>job_function_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>master's</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
-        <is>
-          <t>Master's</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>education_level_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>doctoral</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Doctoral</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>education_level_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>software_development</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>data_analysis</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Data Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>marketing</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>human_resources</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>legal</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>operations</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>job_function_choices</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
